--- a/api/templates/usage_statistics_report/en.xlsx
+++ b/api/templates/usage_statistics_report/en.xlsx
@@ -1,34 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25601"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\ahernandez\repos\aspect\api\templates\usage_statistics_report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48CB0847-83E7-450E-9B38-C5009C9D659F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ECEAD08-64A5-4897-B2E4-9C75E35D03EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="24" windowWidth="23016" windowHeight="12936" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Usage Statistics" sheetId="1" r:id="rId1"/>
+    <sheet name="Usage Totals" sheetId="1" r:id="rId1"/>
+    <sheet name="User Activity" sheetId="2" r:id="rId2"/>
+    <sheet name="Tests by Site" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Usage Statistics'!$A$8:$G$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Usage Totals'!$A$8:$G$8</definedName>
   </definedNames>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
   <si>
     <t>Date Range:  &lt;Dates&gt;</t>
   </si>
@@ -45,42 +55,83 @@
     <t>&lt;Table&gt;</t>
   </si>
   <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>Device Name</t>
-  </si>
-  <si>
-    <t>Module Name</t>
-  </si>
-  <si>
-    <t>Module Serial</t>
-  </si>
-  <si>
-    <t>Last Seen</t>
-  </si>
-  <si>
-    <t>Date Last Issue</t>
-  </si>
-  <si>
-    <t>Last Issue</t>
-  </si>
-  <si>
-    <t>&lt;#&gt;</t>
-  </si>
-  <si>
     <t>Usage Statistics</t>
+  </si>
+  <si>
+    <t>Number of users active during this period</t>
+  </si>
+  <si>
+    <t>Number of SMS messages sent</t>
+  </si>
+  <si>
+    <t>Number of emails sent</t>
+  </si>
+  <si>
+    <t>Number of devices reporting in period</t>
+  </si>
+  <si>
+    <t>Number of tests reported in period</t>
+  </si>
+  <si>
+    <t>Number of tests performed in period</t>
+  </si>
+  <si>
+    <t>&lt;activeUsers&gt;</t>
+  </si>
+  <si>
+    <t>&lt;emailsSent&gt;</t>
+  </si>
+  <si>
+    <t>&lt;devicesReporting&gt;</t>
+  </si>
+  <si>
+    <t>Person Name</t>
+  </si>
+  <si>
+    <t>Last Active</t>
+  </si>
+  <si>
+    <t>List of Users and Sessions</t>
+  </si>
+  <si>
+    <t>Number of Tests by Site</t>
+  </si>
+  <si>
+    <t>Deployment</t>
+  </si>
+  <si>
+    <t># of Tests reported</t>
+  </si>
+  <si>
+    <t># of Tests performed</t>
+  </si>
+  <si>
+    <t>&lt;DateRangeLabel&gt;:  &lt;Dates&gt;</t>
+  </si>
+  <si>
+    <t>&lt;lastActive&gt;</t>
+  </si>
+  <si>
+    <t>&lt;user&gt;</t>
+  </si>
+  <si>
+    <t>&lt;site&gt;</t>
+  </si>
+  <si>
+    <t>&lt;testsReported&gt;</t>
+  </si>
+  <si>
+    <t>&lt;testsPerformed&gt;</t>
+  </si>
+  <si>
+    <t>&lt;smsSent&gt;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
-  </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -93,7 +144,7 @@
       <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -108,6 +159,28 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="3">
@@ -124,7 +197,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -148,43 +221,157 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="thick">
         <color auto="1"/>
       </left>
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin">
+      <top style="thick">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
         <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{D39B92F3-C63D-4BB1-A09E-9572EB61C8C9}"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="MySqlDefault" pivot="0" table="0" count="1" xr9:uid="{F70F115C-7444-4168-AC9A-817454052DD1}">
+      <tableStyleElement type="wholeTable" dxfId="0"/>
+    </tableStyle>
+  </tableStyles>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -561,10 +748,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.5546875" customWidth="1"/>
+    <col min="1" max="1" width="38.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.6640625" customWidth="1"/>
     <col min="3" max="3" width="18.77734375" customWidth="1"/>
     <col min="4" max="4" width="18.44140625" customWidth="1"/>
@@ -573,78 +760,201 @@
     <col min="7" max="7" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="1"/>
+    </row>
+    <row r="2" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="2"/>
+    </row>
+    <row r="3" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2"/>
+    </row>
+    <row r="4" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2"/>
+    </row>
+    <row r="5" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2"/>
+    </row>
+    <row r="7" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="8" spans="1:2" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="1"/>
-    </row>
-    <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="14"/>
+      <c r="B14" s="13"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40AC2301-C80C-4FC7-B9AE-64396E099A82}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="30.77734375" customWidth="1"/>
+    <col min="2" max="2" width="27.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+      <c r="A1" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABE005F9-733A-4A93-ADFC-E0BBDF628800}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="3" width="22.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.4">
+      <c r="A1" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2"/>
-    </row>
-    <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="6"/>
+    <row r="8" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>27</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A8:G9" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/api/templates/usage_statistics_report/en.xlsx
+++ b/api/templates/usage_statistics_report/en.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\ahernandez\repos\aspect\api\templates\usage_statistics_report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ECEAD08-64A5-4897-B2E4-9C75E35D03EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA6B1812-DB3E-4EAF-BEAC-C60C38ECA2BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,10 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
-  <si>
-    <t>Date Range:  &lt;Dates&gt;</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="28">
   <si>
     <t>&lt;StatesLabel&gt;:  &lt;States&gt;</t>
   </si>
@@ -106,9 +103,6 @@
     <t># of Tests performed</t>
   </si>
   <si>
-    <t>&lt;DateRangeLabel&gt;:  &lt;Dates&gt;</t>
-  </si>
-  <si>
     <t>&lt;lastActive&gt;</t>
   </si>
   <si>
@@ -125,6 +119,9 @@
   </si>
   <si>
     <t>&lt;smsSent&gt;</t>
+  </si>
+  <si>
+    <t>Dates:  &lt;Dates&gt;</t>
   </si>
 </sst>
 </file>
@@ -762,81 +759,81 @@
   <sheetData>
     <row r="1" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="3" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B3" s="2"/>
     </row>
     <row r="4" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4" s="2"/>
     </row>
     <row r="5" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" s="2"/>
     </row>
     <row r="7" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="8" spans="1:2" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
@@ -860,33 +857,33 @@
   <sheetData>
     <row r="1" spans="1:2" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="12" t="s">
         <v>15</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -904,54 +901,54 @@
   <sheetData>
     <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="C8" s="12" t="s">
         <v>20</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
         <v>25</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/api/templates/usage_statistics_report/en.xlsx
+++ b/api/templates/usage_statistics_report/en.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25629"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\ahernandez\repos\aspect\api\templates\usage_statistics_report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA6B1812-DB3E-4EAF-BEAC-C60C38ECA2BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AB1FE40-3E7F-43FF-8E16-E6EBE7270455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="29">
   <si>
     <t>&lt;StatesLabel&gt;:  &lt;States&gt;</t>
   </si>
@@ -122,6 +122,9 @@
   </si>
   <si>
     <t>Dates:  &lt;Dates&gt;</t>
+  </si>
+  <si>
+    <t>* You may notice small differences in quantities of devices and results between this report and on screen lists. This is because in order to show the reported results versus performed results, this report is considering the date of creation of the result, instead of the date of completion.</t>
   </si>
 </sst>
 </file>
@@ -312,7 +315,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -346,6 +349,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -745,7 +751,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38.109375" bestFit="1" customWidth="1"/>
@@ -757,38 +763,38 @@
     <col min="7" max="7" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>27</v>
       </c>
       <c r="B2" s="2"/>
     </row>
-    <row r="3" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="2"/>
     </row>
-    <row r="4" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
       <c r="B4" s="2"/>
     </row>
-    <row r="5" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="2"/>
     </row>
-    <row r="7" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="8" spans="1:2" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="8" spans="1:4" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
         <v>5</v>
       </c>
@@ -796,7 +802,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
         <v>6</v>
       </c>
@@ -804,7 +810,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>7</v>
       </c>
@@ -812,7 +818,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>8</v>
       </c>
@@ -820,7 +826,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>9</v>
       </c>
@@ -828,7 +834,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>10</v>
       </c>
@@ -836,11 +842,46 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14"/>
       <c r="B14" s="13"/>
     </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="15"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="15"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="15"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="15"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A15:D19"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>

--- a/api/templates/usage_statistics_report/en.xlsx
+++ b/api/templates/usage_statistics_report/en.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10912"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\ahernandez\repos\aspect\api\templates\usage_statistics_report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mehdi/Desktop/Projects/SystemOne/aspect/api/templates/usage_statistics_report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AB1FE40-3E7F-43FF-8E16-E6EBE7270455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26C88043-4A1A-A24F-8F50-1B1D87F8893C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17400" yWindow="700" windowWidth="34000" windowHeight="25680" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Usage Totals" sheetId="1" r:id="rId1"/>
@@ -25,12 +25,8 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -38,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
   <si>
     <t>&lt;StatesLabel&gt;:  &lt;States&gt;</t>
   </si>
@@ -125,6 +121,12 @@
   </si>
   <si>
     <t>* You may notice small differences in quantities of devices and results between this report and on screen lists. This is because in order to show the reported results versus performed results, this report is considering the date of creation of the result, instead of the date of completion.</t>
+  </si>
+  <si>
+    <t>Page Views</t>
+  </si>
+  <si>
+    <t>&lt;pageView&gt;</t>
   </si>
 </sst>
 </file>
@@ -752,49 +754,49 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D19"/>
-  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="38.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.6640625" customWidth="1"/>
-    <col min="3" max="3" width="18.77734375" customWidth="1"/>
-    <col min="4" max="4" width="18.44140625" customWidth="1"/>
-    <col min="5" max="5" width="16.44140625" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" customWidth="1"/>
+    <col min="4" max="4" width="18.5" customWidth="1"/>
+    <col min="5" max="5" width="16.5" customWidth="1"/>
     <col min="6" max="6" width="21" customWidth="1"/>
     <col min="7" max="7" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>27</v>
       </c>
       <c r="B2" s="2"/>
     </row>
-    <row r="3" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="2"/>
     </row>
-    <row r="4" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>1</v>
       </c>
       <c r="B4" s="2"/>
     </row>
-    <row r="5" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="2"/>
     </row>
-    <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="8" spans="1:4" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:4" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>5</v>
       </c>
@@ -802,7 +804,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
         <v>6</v>
       </c>
@@ -810,7 +812,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>7</v>
       </c>
@@ -818,7 +820,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
         <v>8</v>
       </c>
@@ -826,7 +828,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>9</v>
       </c>
@@ -834,7 +836,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>10</v>
       </c>
@@ -842,11 +844,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A14" s="14"/>
       <c r="B14" s="13"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="15" t="s">
         <v>28</v>
       </c>
@@ -854,25 +856,25 @@
       <c r="C15" s="15"/>
       <c r="D15" s="15"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="15"/>
       <c r="B16" s="15"/>
       <c r="C16" s="15"/>
       <c r="D16" s="15"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="15"/>
       <c r="B17" s="15"/>
       <c r="C17" s="15"/>
       <c r="D17" s="15"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="15"/>
       <c r="B18" s="15"/>
       <c r="C18" s="15"/>
       <c r="D18" s="15"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="15"/>
       <c r="B19" s="15"/>
       <c r="C19" s="15"/>
@@ -889,42 +891,49 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40AC2301-C80C-4FC7-B9AE-64396E099A82}">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30.77734375" customWidth="1"/>
-    <col min="2" max="2" width="27.77734375" customWidth="1"/>
+    <col min="1" max="1" width="30.83203125" customWidth="1"/>
+    <col min="2" max="2" width="27.83203125" customWidth="1"/>
+    <col min="3" max="3" width="27.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C5" s="12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>22</v>
       </c>
       <c r="B6" t="s">
         <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -935,42 +944,42 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABE005F9-733A-4A93-ADFC-E0BBDF628800}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="22.88671875" customWidth="1"/>
+    <col min="1" max="3" width="22.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>18</v>
       </c>
@@ -981,7 +990,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>23</v>
       </c>
